--- a/erp-server/erp-server-file/src/main/resources/excel/workflow/approveSyncRecordExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/workflow/approveSyncRecordExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>通知类型</t>
   </si>
@@ -40,6 +40,9 @@
     <t>单据单号</t>
   </si>
   <si>
+    <t>通知节点</t>
+  </si>
+  <si>
     <t>提醒方式</t>
   </si>
   <si>
@@ -65,6 +68,9 @@
   </si>
   <si>
     <t>{.businessCode}</t>
+  </si>
+  <si>
+    <t>{.noticeNodeName}</t>
   </si>
   <si>
     <t>{.noticeMethodName}</t>
@@ -1049,13 +1055,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="12" width="20.625" customWidth="1"/>
+    <col min="1" max="13" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1083,34 +1089,40 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:9">
+    <row r="2" s="1" customFormat="1" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/workflow/approveSyncRecordExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/workflow/approveSyncRecordExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>通知类型</t>
   </si>
@@ -40,9 +40,6 @@
     <t>单据单号</t>
   </si>
   <si>
-    <t>通知节点</t>
-  </si>
-  <si>
     <t>提醒方式</t>
   </si>
   <si>
@@ -68,9 +65,6 @@
   </si>
   <si>
     <t>{.businessCode}</t>
-  </si>
-  <si>
-    <t>{.noticeNodeName}</t>
   </si>
   <si>
     <t>{.noticeMethodName}</t>
@@ -1055,13 +1049,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="13" width="20.625" customWidth="1"/>
+    <col min="1" max="12" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1089,40 +1083,34 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:9">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:10">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
